--- a/artfynd/A 9599-2025 artfynd.xlsx
+++ b/artfynd/A 9599-2025 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>136134099</v>
       </c>
       <c r="B11" t="n">
-        <v>56935</v>
+        <v>56937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
